--- a/simulacaoes_/custo_robustez_C13/simulacao_rho050/design_variables_statistics.xlsx
+++ b/simulacaoes_/custo_robustez_C13/simulacao_rho050/design_variables_statistics.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variável</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Desvio padrão</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>CV (%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Mínimo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>1º quartil</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>3º quartil</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Máximo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Amplitude</t>
         </is>
@@ -495,31 +483,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>66.61</v>
+        <v>69.88</v>
       </c>
       <c r="D2" t="n">
-        <v>17.61</v>
+        <v>16.73</v>
       </c>
       <c r="E2" t="n">
-        <v>26.43</v>
+        <v>23.94</v>
       </c>
       <c r="F2" t="n">
-        <v>45.69</v>
+        <v>47.77</v>
       </c>
       <c r="G2" t="n">
-        <v>50.94</v>
+        <v>54.68</v>
       </c>
       <c r="H2" t="n">
-        <v>61.28</v>
+        <v>67.03</v>
       </c>
       <c r="I2" t="n">
-        <v>81.37</v>
+        <v>84.44</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>54.31</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +520,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>46.78</v>
+        <v>45.74</v>
       </c>
       <c r="D3" t="n">
-        <v>1.16</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>2.49</v>
+        <v>1.77</v>
       </c>
       <c r="F3" t="n">
-        <v>42.79</v>
+        <v>41.96</v>
       </c>
       <c r="G3" t="n">
-        <v>46.48</v>
+        <v>45.51</v>
       </c>
       <c r="H3" t="n">
-        <v>46.52</v>
+        <v>45.52</v>
       </c>
       <c r="I3" t="n">
-        <v>47.64</v>
+        <v>45.59</v>
       </c>
       <c r="J3" t="n">
-        <v>48.22</v>
+        <v>47.94</v>
       </c>
       <c r="K3" t="n">
-        <v>5.43</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +557,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>8.539999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="D4" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="E4" t="n">
-        <v>18.57</v>
+        <v>17.33</v>
       </c>
       <c r="F4" t="n">
-        <v>6.23</v>
+        <v>6.9</v>
       </c>
       <c r="G4" t="n">
-        <v>7.14</v>
+        <v>7.35</v>
       </c>
       <c r="H4" t="n">
-        <v>8.27</v>
+        <v>8.98</v>
       </c>
       <c r="I4" t="n">
-        <v>10.28</v>
+        <v>10.45</v>
       </c>
       <c r="J4" t="n">
-        <v>11.31</v>
+        <v>11.03</v>
       </c>
       <c r="K4" t="n">
-        <v>5.09</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +594,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>129.58</v>
+        <v>87.06</v>
       </c>
       <c r="D5" t="n">
-        <v>43.96</v>
+        <v>17.68</v>
       </c>
       <c r="E5" t="n">
-        <v>33.92</v>
+        <v>20.31</v>
       </c>
       <c r="F5" t="n">
-        <v>68.88</v>
+        <v>58.24</v>
       </c>
       <c r="G5" t="n">
-        <v>97.59</v>
+        <v>68.77</v>
       </c>
       <c r="H5" t="n">
-        <v>107.16</v>
+        <v>91.7</v>
       </c>
       <c r="I5" t="n">
-        <v>183.21</v>
+        <v>103.25</v>
       </c>
       <c r="J5" t="n">
-        <v>199.71</v>
+        <v>109.14</v>
       </c>
       <c r="K5" t="n">
-        <v>130.83</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +631,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>4.64</v>
+        <v>2.98</v>
       </c>
       <c r="D6" t="n">
-        <v>0.37</v>
+        <v>0.97</v>
       </c>
       <c r="E6" t="n">
-        <v>7.88</v>
+        <v>32.64</v>
       </c>
       <c r="F6" t="n">
-        <v>3.46</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.64</v>
+        <v>2.07</v>
       </c>
       <c r="H6" t="n">
-        <v>4.71</v>
+        <v>2.29</v>
       </c>
       <c r="I6" t="n">
-        <v>4.88</v>
+        <v>3.94</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>4.46</v>
       </c>
       <c r="K6" t="n">
-        <v>1.53</v>
+        <v>2.46</v>
       </c>
     </row>
   </sheetData>

--- a/simulacaoes_/custo_robustez_C13/simulacao_rho050/design_variables_statistics.xlsx
+++ b/simulacaoes_/custo_robustez_C13/simulacao_rho050/design_variables_statistics.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,57 +429,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variável</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Desvio padrão</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CV (%)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Mínimo</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1º quartil</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Mediana</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>3º quartil</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Máximo</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Amplitude</t>
         </is>
@@ -483,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>69.88</v>
+        <v>68.84</v>
       </c>
       <c r="D2" t="n">
-        <v>16.73</v>
+        <v>17.14</v>
       </c>
       <c r="E2" t="n">
-        <v>23.94</v>
+        <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>47.77</v>
+        <v>47.78</v>
       </c>
       <c r="G2" t="n">
-        <v>54.68</v>
+        <v>54.49</v>
       </c>
       <c r="H2" t="n">
-        <v>67.03</v>
+        <v>64.89</v>
       </c>
       <c r="I2" t="n">
-        <v>84.44</v>
+        <v>82.72</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>52.23</v>
+        <v>52.22</v>
       </c>
     </row>
     <row r="3">
@@ -520,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>45.74</v>
+        <v>45.58</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>1.77</v>
+        <v>0.44</v>
       </c>
       <c r="F3" t="n">
-        <v>41.96</v>
+        <v>45.5</v>
       </c>
       <c r="G3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="I3" t="n">
         <v>45.51</v>
       </c>
-      <c r="H3" t="n">
-        <v>45.52</v>
-      </c>
-      <c r="I3" t="n">
-        <v>45.59</v>
-      </c>
       <c r="J3" t="n">
-        <v>47.94</v>
+        <v>46.6</v>
       </c>
       <c r="K3" t="n">
-        <v>5.99</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -557,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>8.92</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="E4" t="n">
-        <v>17.33</v>
+        <v>17.92</v>
       </c>
       <c r="F4" t="n">
-        <v>6.9</v>
+        <v>6.99</v>
       </c>
       <c r="G4" t="n">
-        <v>7.35</v>
+        <v>7.34</v>
       </c>
       <c r="H4" t="n">
-        <v>8.98</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>10.45</v>
+        <v>10.68</v>
       </c>
       <c r="J4" t="n">
-        <v>11.03</v>
+        <v>11.39</v>
       </c>
       <c r="K4" t="n">
-        <v>4.13</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="5">
@@ -594,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>87.06</v>
+        <v>87.64</v>
       </c>
       <c r="D5" t="n">
-        <v>17.68</v>
+        <v>17.9</v>
       </c>
       <c r="E5" t="n">
-        <v>20.31</v>
+        <v>20.43</v>
       </c>
       <c r="F5" t="n">
-        <v>58.24</v>
+        <v>58.55</v>
       </c>
       <c r="G5" t="n">
-        <v>68.77</v>
+        <v>69.5</v>
       </c>
       <c r="H5" t="n">
-        <v>91.7</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>103.25</v>
+        <v>103.23</v>
       </c>
       <c r="J5" t="n">
-        <v>109.14</v>
+        <v>120.72</v>
       </c>
       <c r="K5" t="n">
-        <v>50.91</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="6">
@@ -631,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>2.98</v>
+        <v>3.44</v>
       </c>
       <c r="D6" t="n">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="E6" t="n">
-        <v>32.64</v>
+        <v>33.14</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="H6" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>3.94</v>
+        <v>4.68</v>
       </c>
       <c r="J6" t="n">
-        <v>4.46</v>
+        <v>4.98</v>
       </c>
       <c r="K6" t="n">
-        <v>2.46</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>
